--- a/bulk_employee_sample.xlsx
+++ b/bulk_employee_sample.xlsx
@@ -397,19 +397,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:L11"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" customWidth="1"/>
+    <col min="2" max="2" width="36.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="22.83203125" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -420,386 +421,419 @@
         <v>email</v>
       </c>
       <c r="C1" t="str">
+        <v>password</v>
+      </c>
+      <c r="D1" t="str">
         <v>mobile_number</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>date_of_birth</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>gender</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>pan_number</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>aadhaar_number</v>
       </c>
-      <c r="H1" t="str">
-        <v>password</v>
-      </c>
       <c r="I1" t="str">
+        <v>designation</v>
+      </c>
+      <c r="J1" t="str">
         <v>role</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>department</v>
       </c>
-      <c r="K1" t="str">
-        <v>reporting_to</v>
+      <c r="L1" t="str">
+        <v>tier_id</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Rahul Sharma</v>
+        <v>Karthik Subramanian</v>
       </c>
       <c r="B2" t="str">
-        <v>rahul.sharma@company.in</v>
+        <v>karthik.subramanian@company.in</v>
       </c>
       <c r="C2" t="str">
-        <v>9876543210</v>
+        <v>Pass@123</v>
       </c>
       <c r="D2" t="str">
-        <v>1995-03-15</v>
+        <v>9711200001</v>
       </c>
       <c r="E2" t="str">
+        <v>1994-02-19</v>
+      </c>
+      <c r="F2" t="str">
         <v>Male</v>
       </c>
-      <c r="F2" t="str">
-        <v>ABCDE1234F</v>
-      </c>
       <c r="G2" t="str">
-        <v>123456789012</v>
+        <v>KARTH1101A</v>
       </c>
       <c r="H2" t="str">
-        <v>pass123</v>
+        <v>200000000001</v>
       </c>
       <c r="I2" t="str">
+        <v>Software Engineer</v>
+      </c>
+      <c r="J2" t="str">
         <v>Employee</v>
       </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
         <v>Engineering</v>
       </c>
-      <c r="K2" t="str">
-        <v>Ravi Kumar</v>
+      <c r="L2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Priya Nair</v>
+        <v>Meera Bhatia</v>
       </c>
       <c r="B3" t="str">
-        <v>priya.nair@company.in</v>
+        <v>meera.bhatia@company.in</v>
       </c>
       <c r="C3" t="str">
-        <v>9876543211</v>
+        <v>Pass@123</v>
       </c>
       <c r="D3" t="str">
-        <v>1992-08-22</v>
+        <v>9711200002</v>
       </c>
       <c r="E3" t="str">
+        <v>1990-05-08</v>
+      </c>
+      <c r="F3" t="str">
         <v>Female</v>
       </c>
-      <c r="F3" t="str">
-        <v>FGHIJ5678K</v>
-      </c>
       <c r="G3" t="str">
-        <v>234567890123</v>
+        <v>MEERA2202B</v>
       </c>
       <c r="H3" t="str">
-        <v>pass123</v>
+        <v>200000000002</v>
       </c>
       <c r="I3" t="str">
         <v>Tech Lead</v>
       </c>
       <c r="J3" t="str">
-        <v>Design</v>
+        <v>Request Approver</v>
       </c>
       <c r="K3" t="str">
-        <v>Ravi Kumar</v>
+        <v>Engineering</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Vikram Patel</v>
+        <v>Rajesh Kumar</v>
       </c>
       <c r="B4" t="str">
-        <v>vikram.patel@company.in</v>
+        <v>rajesh.kumar@company.in</v>
       </c>
       <c r="C4" t="str">
-        <v>9876543212</v>
+        <v>Pass@123</v>
       </c>
       <c r="D4" t="str">
-        <v>1990-01-10</v>
+        <v>9711200003</v>
       </c>
       <c r="E4" t="str">
+        <v>1985-09-23</v>
+      </c>
+      <c r="F4" t="str">
         <v>Male</v>
       </c>
-      <c r="F4" t="str">
-        <v>KLMNO9012P</v>
-      </c>
       <c r="G4" t="str">
-        <v>345678901234</v>
+        <v>RAJES3303C</v>
       </c>
       <c r="H4" t="str">
-        <v>pass123</v>
+        <v>200000000003</v>
       </c>
       <c r="I4" t="str">
-        <v>Employee</v>
+        <v>Manager</v>
       </c>
       <c r="J4" t="str">
-        <v>Marketing</v>
+        <v>Request Approver</v>
       </c>
       <c r="K4" t="str">
-        <v>Deepa Krishnan</v>
+        <v>Operations</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Ananya Reddy</v>
+        <v>Sneha Verma</v>
       </c>
       <c r="B5" t="str">
-        <v>ananya.reddy@company.in</v>
+        <v>sneha.verma@company.in</v>
       </c>
       <c r="C5" t="str">
-        <v>9876543213</v>
+        <v>Pass@123</v>
       </c>
       <c r="D5" t="str">
-        <v>1998-11-05</v>
+        <v>9711200004</v>
       </c>
       <c r="E5" t="str">
+        <v>1996-11-12</v>
+      </c>
+      <c r="F5" t="str">
         <v>Female</v>
       </c>
-      <c r="F5" t="str">
-        <v>PQRST3456U</v>
-      </c>
       <c r="G5" t="str">
-        <v>456789012345</v>
+        <v>SNEHA4404D</v>
       </c>
       <c r="H5" t="str">
-        <v>pass123</v>
+        <v>200000000004</v>
       </c>
       <c r="I5" t="str">
-        <v>Finance</v>
+        <v>Software Engineer</v>
       </c>
       <c r="J5" t="str">
-        <v>Finance</v>
+        <v>Employee</v>
       </c>
       <c r="K5" t="str">
-        <v>Anil Menon</v>
+        <v>Engineering</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Karthik Iyer</v>
+        <v>Aditya Khanna</v>
       </c>
       <c r="B6" t="str">
-        <v>karthik.iyer@company.in</v>
+        <v>aditya.khanna@company.in</v>
       </c>
       <c r="C6" t="str">
-        <v>9876543214</v>
+        <v>Pass@123</v>
       </c>
       <c r="D6" t="str">
-        <v>1993-06-18</v>
+        <v>9711200005</v>
       </c>
       <c r="E6" t="str">
+        <v>1995-07-04</v>
+      </c>
+      <c r="F6" t="str">
         <v>Male</v>
       </c>
-      <c r="F6" t="str">
-        <v>UVWXY7890Z</v>
-      </c>
       <c r="G6" t="str">
-        <v>567890123456</v>
+        <v>ADITY5505E</v>
       </c>
       <c r="H6" t="str">
-        <v>pass123</v>
+        <v>200000000005</v>
       </c>
       <c r="I6" t="str">
+        <v>Software Engineer</v>
+      </c>
+      <c r="J6" t="str">
         <v>Employee</v>
       </c>
-      <c r="J6" t="str">
-        <v>Operations</v>
-      </c>
       <c r="K6" t="str">
-        <v>Ravi Kumar</v>
+        <v>QA</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Meera Gupta</v>
+        <v>Pooja Desai</v>
       </c>
       <c r="B7" t="str">
-        <v>meera.gupta@company.in</v>
+        <v>pooja.desai@company.in</v>
       </c>
       <c r="C7" t="str">
-        <v>9876543215</v>
+        <v>Pass@123</v>
       </c>
       <c r="D7" t="str">
-        <v>1996-04-25</v>
+        <v>9711200006</v>
       </c>
       <c r="E7" t="str">
+        <v>1988-03-30</v>
+      </c>
+      <c r="F7" t="str">
         <v>Female</v>
       </c>
-      <c r="F7" t="str">
-        <v>BCDEF2345G</v>
-      </c>
       <c r="G7" t="str">
-        <v>678901234567</v>
+        <v>POOJA6606F</v>
       </c>
       <c r="H7" t="str">
-        <v>pass123</v>
+        <v>200000000006</v>
       </c>
       <c r="I7" t="str">
-        <v>Employee</v>
+        <v>Finance</v>
       </c>
       <c r="J7" t="str">
-        <v>HR</v>
+        <v>Finance</v>
       </c>
       <c r="K7" t="str">
-        <v>Deepa Krishnan</v>
+        <v>Finance</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Sanjay Das</v>
+        <v>Nikhil Shenoy</v>
       </c>
       <c r="B8" t="str">
-        <v>sanjay.das@company.in</v>
+        <v>nikhil.shenoy@company.in</v>
       </c>
       <c r="C8" t="str">
-        <v>9876543216</v>
+        <v>Pass@123</v>
       </c>
       <c r="D8" t="str">
-        <v>1988-12-30</v>
+        <v>9711200007</v>
       </c>
       <c r="E8" t="str">
+        <v>1987-01-17</v>
+      </c>
+      <c r="F8" t="str">
         <v>Male</v>
       </c>
-      <c r="F8" t="str">
-        <v>GHIJK6789L</v>
-      </c>
       <c r="G8" t="str">
-        <v>789012345678</v>
+        <v>NIKHI7707G</v>
       </c>
       <c r="H8" t="str">
-        <v>pass123</v>
+        <v>200000000007</v>
       </c>
       <c r="I8" t="str">
         <v>Manager</v>
       </c>
       <c r="J8" t="str">
+        <v>Request Approver</v>
+      </c>
+      <c r="K8" t="str">
         <v>Engineering</v>
       </c>
-      <c r="K8" t="str">
+      <c r="L8" t="str">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Lakshmi Pillai</v>
+        <v>Tanvi Saxena</v>
       </c>
       <c r="B9" t="str">
-        <v>lakshmi.pillai@company.in</v>
+        <v>tanvi.saxena@company.in</v>
       </c>
       <c r="C9" t="str">
-        <v>9876543217</v>
+        <v>Pass@123</v>
       </c>
       <c r="D9" t="str">
-        <v>1994-07-14</v>
+        <v>9711200008</v>
       </c>
       <c r="E9" t="str">
+        <v>1998-08-25</v>
+      </c>
+      <c r="F9" t="str">
         <v>Female</v>
       </c>
-      <c r="F9" t="str">
-        <v>LMNOP1234Q</v>
-      </c>
       <c r="G9" t="str">
-        <v>890123456789</v>
+        <v>TANVI8808H</v>
       </c>
       <c r="H9" t="str">
-        <v>pass123</v>
+        <v>200000000008</v>
       </c>
       <c r="I9" t="str">
+        <v>Software Engineer</v>
+      </c>
+      <c r="J9" t="str">
         <v>Employee</v>
       </c>
-      <c r="J9" t="str">
-        <v>QA</v>
-      </c>
       <c r="K9" t="str">
-        <v>Sanjay Das</v>
+        <v>Engineering</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Arjun Verma</v>
+        <v>Rohit Bhattacharya</v>
       </c>
       <c r="B10" t="str">
-        <v>arjun.verma@company.in</v>
+        <v>rohit.bhattacharya@company.in</v>
       </c>
       <c r="C10" t="str">
-        <v>9876543218</v>
+        <v>Pass@123</v>
       </c>
       <c r="D10" t="str">
-        <v>1991-09-02</v>
+        <v>9711200009</v>
       </c>
       <c r="E10" t="str">
+        <v>1991-04-14</v>
+      </c>
+      <c r="F10" t="str">
         <v>Male</v>
       </c>
-      <c r="F10" t="str">
-        <v>QRSTU5678V</v>
-      </c>
       <c r="G10" t="str">
-        <v>901234567890</v>
+        <v>ROHIT9909J</v>
       </c>
       <c r="H10" t="str">
-        <v>pass123</v>
+        <v>200000000009</v>
       </c>
       <c r="I10" t="str">
-        <v>Employee</v>
+        <v>Tech Lead</v>
       </c>
       <c r="J10" t="str">
-        <v>DevOps</v>
+        <v>Request Approver</v>
       </c>
       <c r="K10" t="str">
-        <v>Karthik Iyer</v>
+        <v>Engineering</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Sneha Mishra</v>
+        <v>Lavanya Krishnamurthy</v>
       </c>
       <c r="B11" t="str">
-        <v>sneha.mishra@company.in</v>
+        <v>lavanya.krishnamurthy@company.in</v>
       </c>
       <c r="C11" t="str">
-        <v>9876543219</v>
+        <v>Pass@123</v>
       </c>
       <c r="D11" t="str">
-        <v>1997-02-28</v>
+        <v>9711200010</v>
       </c>
       <c r="E11" t="str">
+        <v>1997-12-02</v>
+      </c>
+      <c r="F11" t="str">
         <v>Female</v>
       </c>
-      <c r="F11" t="str">
-        <v>VWXYZ9012A</v>
-      </c>
       <c r="G11" t="str">
-        <v>012345678901</v>
+        <v>LAVAN1010K</v>
       </c>
       <c r="H11" t="str">
-        <v>pass123</v>
+        <v>200000000010</v>
       </c>
       <c r="I11" t="str">
+        <v>Software Engineer</v>
+      </c>
+      <c r="J11" t="str">
         <v>Employee</v>
       </c>
-      <c r="J11" t="str">
-        <v>Support</v>
-      </c>
       <c r="K11" t="str">
-        <v>Deepa Krishnan</v>
+        <v>Design</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>